--- a/site/HR-ITSM-NinjaOne-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-NinjaOne-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,776 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01M65KHYGNNK9126VWXMCRB1JM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65KHYGNNK9126VWXMCRB1JM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01M65KN1F03GPB5AXCCZT9N51R</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65KN1F03GPB5AXCCZT9N51R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01M65KZS4Q5GFGP3X1JEZVMHA2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65KZS4Q5GFGP3X1JEZVMHA2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01M65M39MN6GS1J18XXRFTAM9H</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65M39MN6GS1J18XXRFTAM9H</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01M65M45485SAH0DA868B9DE7F</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65M45485SAH0DA868B9DE7F</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01M65R51T1EY7710P8JM76T2WS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65R51T1EY7710P8JM76T2WS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M65R5P2834QCADF11QEPGG0T</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65R5P2834QCADF11QEPGG0T</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M65R710DZT360Z99CEBTN97C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65R710DZT360Z99CEBTN97C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Filter Employees</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M65R93AKS2AA5KCR2QJJA49G</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65R93AKS2AA5KCR2QJJA49G</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Employee Filter Configuration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M65RAYA2XSB1YQ9F4PM17XP1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RAYA2XSB1YQ9F4PM17XP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Service Desk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M65RHWHDM89QM1A57A10DPVA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RHWHDM89QM1A57A10DPVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01M65RKJ9F4TGEYVA3CXD24MRS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RKJ9F4TGEYVA3CXD24MRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Desk Application Configuration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M65RN7EFJSRKK58MAXSCSHAX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RN7EFJSRKK58MAXSCSHAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Messaging Application</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M65RQP800726K6QH0000XBB7</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RQP800726K6QH0000XBB7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JML Ticket Creation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M65RRCWDEMWKZ5ZRFVJFSAJC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RRCWDEMWKZ5ZRFVJFSAJC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ticket Creation Configuration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M65RTKGSX479HHXRGJ98WNBC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65RTKGSX479HHXRGJ98WNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M65TM2JVZG3CHVJ7BVEPPWQJ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65TM2JVZG3CHVJ7BVEPPWQJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M65TPRT0W0SHRCNGPA5TC3X2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65TPRT0W0SHRCNGPA5TC3X2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Define Notification Channel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01M65TPX4QBMSBNWPVQR7DZP1H</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65TPX4QBMSBNWPVQR7DZP1H</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M65TQSJH9ESTN2Q46S7PQ3H4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65TQSJH9ESTN2Q46S7PQ3H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Global Operation Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01M65ZBE8Z9Z7TPY7FK9W488Y7</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZBE8Z9Z7TPY7FK9W488Y7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M65ZCAY3QJ8CMK7YMJWQ28HG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZCAY3QJ8CMK7YMJWQ28HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01M65ZDPN5BNWRS4E40W2RBHPJ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZDPN5BNWRS4E40W2RBHPJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Operating Safeguard Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M65ZE83M03K9ZJQ50P91KF22</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZE83M03K9ZJQ50P91KF22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01M65ZGJ6HDKJ9ZZNHNHBBGH8Q</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZGJ6HDKJ9ZZNHNHBBGH8Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Service Desk Bridge</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01M65ZH8K1K1AWKF5JGNQ2ZHFA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZH8K1K1AWKF5JGNQ2ZHFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01M65ZHSR54MKVR3XADCRWXE47</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZHSR54MKVR3XADCRWXE47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01M65ZM7ZRJTEPQVHR9B7VZMP1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZM7ZRJTEPQVHR9B7VZMP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Supported Attributes for Change event</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01M65ZN5J14JNSWYT5H3FEYFQ7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-NinjaOne-Integration-Guide/#h_01M65ZN5J14JNSWYT5H3FEYFQ7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
